--- a/data/trans_orig/RUIDO_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Clase-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4478</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>8347</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12286</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>16473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>16357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15274</t>
+          <t>15450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29646</t>
+          <t>29329</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27517</t>
+          <t>27865</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39009</t>
+          <t>39070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>41884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56162</t>
+          <t>56379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73032</t>
+          <t>73632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92013</t>
+          <t>91611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2328</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>589</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>430</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6559</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32358</t>
+          <t>32377</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41547</t>
+          <t>41490</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32737</t>
+          <t>33078</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42856</t>
+          <t>42407</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>67837</t>
+          <t>68752</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>82288</t>
+          <t>82369</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>498</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>15026</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>14079</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>20770</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22710</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32970</t>
+          <t>32798</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>39988</t>
+          <t>39835</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>52015</t>
+          <t>51895</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -4845,12 +4845,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>918</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>864</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>4523</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>304</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>6061</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>566</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>270</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>478</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>25835</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>15479</t>
+          <t>15275</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>38016</t>
+          <t>37224</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>89944</t>
+          <t>90401</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>110341</t>
+          <t>110974</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>62852</t>
+          <t>63366</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>84824</t>
+          <t>85262</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>159680</t>
+          <t>160072</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>192207</t>
+          <t>193394</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>13864</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>776</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>15920</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>35930</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>44860</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>52011</t>
+          <t>51631</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>66040</t>
+          <t>65199</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>90899</t>
+          <t>91572</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>107305</t>
+          <t>107260</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>813</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8547,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>13559</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>19476</t>
+          <t>20208</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>27778</t>
+          <t>28021</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>26744</t>
+          <t>26758</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>36179</t>
+          <t>36145</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>50452</t>
+          <t>49629</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>62458</t>
+          <t>61871</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -8890,12 +8890,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>382</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8925,12 +8925,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -9455,12 +9455,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>8415</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>20533</t>
+          <t>20188</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9618,47 +9618,47 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>19475</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>11757</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>30089</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
           <t>1,66%</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R82" s="2" t="inlineStr">
-        <is>
-          <t>19475</t>
-        </is>
-      </c>
-      <c r="S82" s="2" t="inlineStr">
-        <is>
-          <t>11927</t>
-        </is>
-      </c>
-      <c r="T82" s="2" t="inlineStr">
-        <is>
-          <t>29998</t>
-        </is>
-      </c>
-      <c r="U82" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="V82" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>23533</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>31365</t>
+          <t>31931</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>28168</t>
+          <t>28713</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>50227</t>
+          <t>50282</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>26979</t>
+          <t>27481</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>48034</t>
+          <t>48907</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9922,12 +9922,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>31455</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>60043</t>
+          <t>57915</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9957,12 +9957,12 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>62620</t>
+          <t>63963</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>96736</t>
+          <t>96507</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>239294</t>
+          <t>240636</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>273873</t>
+          <t>273230</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10035,12 +10035,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>266680</t>
+          <t>267597</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>300376</t>
+          <t>300609</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>516831</t>
+          <t>516359</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>565561</t>
+          <t>563799</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>998</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>366</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>569</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -946,82 +946,82 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5196</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1059,82 +1059,82 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2081</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>323</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5167</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>777</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>777</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>860</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6350</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>918</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -1511,47 +1511,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5584</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4100</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>530</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10590</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16357</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21706</t>
+          <t>22579</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29329</t>
+          <t>31581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -1850,72 +1850,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>46530</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39154</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>52541</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>33601</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>27865</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>39070</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>62,12%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49797</t>
+          <t>33486</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41884</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56379</t>
+          <t>39560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>83399</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73632</t>
+          <t>71211</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91611</t>
+          <t>88654</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -1963,74 +1963,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>68583</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>54088</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>54689</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>54689</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>54689</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>72528</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>72528</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>72528</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>178</t>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>126616</t>
+          <t>123272</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2328</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>382</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2419,72 +2419,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>342</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>342</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>953</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -2645,82 +2645,82 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>957</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>4629</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>9,5%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>957</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -2758,47 +2758,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3207</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5297</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,94%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2871,47 +2871,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4060</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>360</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -2984,72 +2984,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2545</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6177</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>13,12%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2140</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5166</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>738</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -3097,72 +3097,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4901</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1864</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>9450</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20,08%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>4321</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>8297</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>8079</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>15290</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -3210,72 +3210,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>36722</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>30761</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>41228</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>78,03%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>65,36%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>87,6%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>37418</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>32377</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>41490</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>77,25%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>66,84%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>85,66%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>37791</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>31787</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42407</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>75790</t>
+          <t>74512</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>68752</t>
+          <t>67003</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>82369</t>
+          <t>80899</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -3323,74 +3323,74 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>47064</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>48438</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>49093</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>49093</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>49093</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>48755</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>48755</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>48755</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>142</t>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>97194</t>
+          <t>96156</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3440,72 +3440,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4218</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>17,24%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>751</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -3892,82 +3892,82 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>6836</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -4118,72 +4118,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>845</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>845</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -4344,72 +4344,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2298</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>6066</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>18,53%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -4457,72 +4457,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>5284</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2539</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>9147</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>16,14%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>27,94%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>3778</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>1747</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>7054</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>28,83%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -4570,72 +4570,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>24157</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>19408</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>27822</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>73,78%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>59,28%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>84,98%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>17879</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>14079</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>20770</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>73,08%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>57,55%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>84,9%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>13757</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>32798</t>
+          <t>20576</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>41661</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>39835</t>
+          <t>35531</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>51895</t>
+          <t>46415</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -4683,74 +4683,74 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>32741</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>24110</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>24110</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>24110</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>38059</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>38059</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>38059</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>88</t>
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,107 +4800,107 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>2949</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>8708</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>644</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>860</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -5252,82 +5252,82 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>962</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>4335</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>962</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -5365,72 +5365,72 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>6426</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>486</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,32 +5440,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>497</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5478,47 +5478,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>4731</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>6643</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>244</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -5591,72 +5591,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>5479</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>1635</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>5195</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>326</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>8645</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -5704,72 +5704,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>9735</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>5241</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>17760</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>9,97%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>4551</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>1406</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>9535</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>18237</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -5817,72 +5817,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>10297</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>4980</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>25893</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>26,52%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>9102</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>4081</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>15275</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>37224</t>
+          <t>33028</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -5930,72 +5930,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>70283</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>58614</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>77958</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>71,97%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>60,02%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>79,83%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>100171</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>90401</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>110974</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>83,36%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>75,23%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>76464</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>63366</t>
+          <t>63295</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>85262</t>
+          <t>76523</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>176636</t>
+          <t>140939</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>160072</t>
+          <t>127373</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>193394</t>
+          <t>150809</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>80,03%</t>
         </is>
       </c>
     </row>
@@ -6043,74 +6043,74 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>97653</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>120162</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>90791</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>90791</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>90791</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>105894</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>105894</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>105894</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>285</t>
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>226056</t>
+          <t>188444</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6273,82 +6273,82 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>891</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>4739</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>891</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -6612,82 +6612,82 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>4584</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>944</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -6725,82 +6725,82 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>877</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>3968</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>877</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -6838,72 +6838,72 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>8452</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>5584</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>9220</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -7069,102 +7069,102 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>571</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>2574</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>6286</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>13,44%</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>4357</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>1807</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>8457</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
           <t>1,56%</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>2751</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>8271</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>5703</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="inlineStr">
-        <is>
-          <t>11586</t>
-        </is>
-      </c>
-      <c r="U60" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -7177,72 +7177,72 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>4498</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>8466</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>12,29%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>5310</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>2542</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>10014</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>15284</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -7290,72 +7290,72 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>56682</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>49653</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>61027</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>82,31%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>72,11%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>88,62%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>40933</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>35930</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>44860</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>81,47%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>71,51%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>89,29%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>59843</t>
+          <t>37776</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>51631</t>
+          <t>33026</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>65199</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>100776</t>
+          <t>94457</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>91572</t>
+          <t>87054</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>107260</t>
+          <t>100756</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -7403,74 +7403,74 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>68862</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>50242</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>46778</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>46778</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>46778</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>74439</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>74439</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>74439</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>177</t>
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>124681</t>
+          <t>115640</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -8198,72 +8198,72 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>3210</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>8915</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>23,9%</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>5878</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>8653</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -8424,72 +8424,72 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>4792</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>15,51%</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -8537,72 +8537,72 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>4635</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1795</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>8712</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>12,43%</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>23,36%</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>3409</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>7371</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>3538</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>1271</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>7291</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
         <is>
           <t>11,04%</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>23,86%</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>4587</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>8642</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8612,32 +8612,32 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -8655,32 +8655,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>24050</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>28021</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8690,32 +8690,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>25491</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>36145</t>
+          <t>28937</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>56953</t>
+          <t>54946</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>49629</t>
+          <t>48579</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>61871</t>
+          <t>60807</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -8763,74 +8763,74 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>37299</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>30892</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>32047</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>32047</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>32047</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="P75" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>40230</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>40230</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr">
-        <is>
-          <t>40230</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>95</t>
@@ -8838,17 +8838,17 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>71122</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8880,72 +8880,72 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>3815</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>9371</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>4142</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4182</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>0,12%</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>4026</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>9606</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8955,27 +8955,27 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -8993,72 +8993,72 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>5998</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>1538</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>5502</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9068,32 +9068,32 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>8868</t>
+          <t>8397</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -9106,82 +9106,82 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>4800</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
@@ -9191,12 +9191,12 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>342</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -9269,49 +9269,49 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R79" s="2" t="inlineStr">
-        <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="S79" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T79" s="2" t="inlineStr">
-        <is>
-          <t>2909</t>
-        </is>
-      </c>
-      <c r="U79" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -9332,72 +9332,72 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>3862</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>4768</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -9445,72 +9445,72 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>3780</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>9740</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>3408</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>7905</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9520,32 +9520,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>13525</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -9558,72 +9558,72 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>9780</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>5100</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>17769</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>8069</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>3723</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>15239</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>16325</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9633,32 +9633,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>18390</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>11362</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>30089</t>
+          <t>28606</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -9671,72 +9671,72 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>3502</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>8443</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>7989</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9746,32 +9746,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>13218</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -9784,72 +9784,72 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>19820</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>12768</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>28867</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>15930</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>9942</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>23881</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>21932</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>31931</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9859,32 +9859,32 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>37862</t>
+          <t>35468</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>28713</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>50282</t>
+          <t>48313</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -9897,72 +9897,72 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>40429</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>31254</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>54511</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>15,48%</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>37037</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>27481</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>48907</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>38300</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>29974</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>57915</t>
+          <t>48093</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9972,32 +9972,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>78394</t>
+          <t>78728</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>63963</t>
+          <t>66418</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>96507</t>
+          <t>95674</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -10010,72 +10010,72 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>263828</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>247704</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>277589</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>74,91%</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>70,33%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>78,82%</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>254672</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>240636</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>273230</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>73,3%</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>83,23%</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>285302</t>
+          <t>222704</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>267597</t>
+          <t>208620</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>300609</t>
+          <t>234148</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10085,32 +10085,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>539974</t>
+          <t>486531</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>516359</t>
+          <t>467082</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>563799</t>
+          <t>504944</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>77,72%</t>
         </is>
       </c>
     </row>
@@ -10123,74 +10123,74 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>352202</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
           <t>463</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>328286</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>297508</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>297508</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>297508</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="P87" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>379906</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>379906</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>379906</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
           <t>965</t>
@@ -10198,17 +10198,17 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>708192</t>
+          <t>649709</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
